--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2021_antofagasta.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2021_antofagasta.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:21</t>
+    <t xml:space="preserve">2026-09-24 01:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -570,7 +570,7 @@
         <v>-0.15</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>0.35</v>
@@ -590,10 +590,10 @@
         <v>7</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-0.24</v>
+        <v>-0.25</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>0.01</v>
@@ -616,7 +616,7 @@
         <v>-0.05</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>0.26</v>
@@ -630,7 +630,7 @@
         <v>8</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>-0.4</v>
+        <v>-0.41</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>7</v>
@@ -639,7 +639,7 @@
         <v>0.22</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>-0.62</v>
@@ -662,10 +662,10 @@
         <v>0.26</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>-0.37</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="7">
@@ -676,19 +676,19 @@
         <v>14</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>9</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="8">
@@ -699,19 +699,19 @@
         <v>14</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>-0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>9</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.14</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="9">
@@ -722,19 +722,19 @@
         <v>14</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>9</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-0.16</v>
+        <v>-0.15</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="10">
@@ -749,10 +749,10 @@
         <v>3</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="G10" s="2"/>
     </row>
@@ -768,10 +768,10 @@
         <v>3</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="G11" s="2"/>
     </row>
@@ -789,13 +789,13 @@
         <v>7</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0.07</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="13">
@@ -812,13 +812,13 @@
         <v>7</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.07</v>
+        <v>0.08</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="14">
@@ -829,19 +829,19 @@
         <v>14</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.05</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>8</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>-0.24</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="15">
@@ -852,19 +852,19 @@
         <v>14</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>8</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>-0.13</v>
+        <v>-0.08</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.24</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="16">
@@ -875,16 +875,16 @@
         <v>14</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>9</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>0.41</v>
@@ -898,16 +898,16 @@
         <v>14</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>0.39</v>
+        <v>0.41</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>9</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>-0.11</v>
+        <v>-0.09</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>0.5</v>
@@ -930,7 +930,7 @@
         <v>-0.41</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>-0.14</v>
@@ -953,7 +953,7 @@
         <v>-0.2</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>0.41</v>
@@ -973,13 +973,13 @@
         <v>7</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="21">
@@ -990,7 +990,7 @@
         <v>31</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>-0.44</v>
+        <v>-0.46</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>9</v>
@@ -999,10 +999,10 @@
         <v>0.06</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>-0.5</v>
+        <v>-0.52</v>
       </c>
     </row>
     <row r="22">
@@ -1013,19 +1013,19 @@
         <v>31</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>-0.69</v>
+        <v>-0.68</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>9</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>-0.11</v>
+        <v>-0.12</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>-0.58</v>
+        <v>-0.56</v>
       </c>
     </row>
     <row r="23">
@@ -1042,13 +1042,13 @@
         <v>9</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>-0.16</v>
+        <v>-0.15</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2021_antofagasta.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2021_antofagasta.xlsx
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:12</t>
+    <t xml:space="preserve">2026-10-01 23:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2021_antofagasta.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2021_antofagasta.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:06</t>
+    <t xml:space="preserve">2026-10-05 19:45</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
